--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_final(4).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_final(4).xlsx
@@ -9,10 +9,10 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="20070" windowHeight="9540"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
-    <sheet name="圣诺汀之梦_终局（终）" sheetId="1" r:id="rId1"/>
+    <sheet name="圣诺汀之梦_终局（终） (1)" sheetId="1" r:id="rId1"/>
     <sheet name="转换说明" sheetId="2" r:id="rId2"/>
     <sheet name="命令库" sheetId="3" r:id="rId3"/>
   </sheets>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1401" uniqueCount="477">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1401" uniqueCount="480">
   <si>
     <t>ID</t>
   </si>
@@ -96,8 +96,309 @@
     <t>面对摆在眼前的两个按钮，你的最终决定是？</t>
   </si>
   <si>
+    <t>源类型=type:txt_pb; 层级=1</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>choice(选择克拉克|jump(7))&amp;choice(选择亚波伦|jump(55))</t>
+  </si>
+  <si>
+    <t>源类型=type:selectBC; 层级=2</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=3</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">你的指尖落在右侧的按钮上，不带一丝犹豫。 </t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=4</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>按下去的那一瞬间，你能感觉到整个房间都安静了一瞬——连亚波伦脸上的笑意都暂停了半秒。然后，电流声随之响起。如同某种无法避免、亦无法延迟的天罚，降临在了那个操弄人心的魔鬼身上。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=5</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>亚波伦的身体猛地一弓，喉间滚出一声压抑的闷哼，巨大的能量波动席卷了他的身体，顺着整间手术室的墙壁扩散开来，惨白的灯光开始疯狂闪烁，每一次明暗交替都带着电流滋啦的炸响。</t>
+  </si>
+  <si>
+    <t>playsfx(ElectricShock)&amp;bgfade(sntzm_final(3)_57,1)</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=6</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>这个一直以来从容不迫的男人，这一刻也终于露出了痛苦的表情，但他没有惨叫或是哀嚎，反而以一种解脱般的狂喜，轻轻哼唱起了《匹诺曹》的童谣。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=7</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>亚波伦</t>
+  </si>
+  <si>
+    <t>我曾被束缚，但现在自由了......我已无拘无束。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_Abaddon; 层级=8</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>他的声音在电流的杂音中断断续续地传出来，清晰、平静，像是正在经历某种他早就知晓结局的超凡仪式。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=9</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">但最终，这首在死神面前奏响的终曲也还是随着其身体机能的失控，逐渐消减、失真、融化，直到完全消失在持续的白噪音里。 </t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=10</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>你听到右侧隔间的灯光暗了一档。门锁解除的声音在同一刻响起——咔哒一声，像是某个被拧紧的阀门突然松动了一下。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=11</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">你转过头，看见左侧隔间的铁门正在缓缓弹开，克拉克还坐在那把电椅上，但他的头已经微微抬起，目光模糊地穿过你们之间那段被灯光切割成两半的距离。 </t>
+  </si>
+  <si>
+    <t>bgfade(sntzm_final(4)_15,1)</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=12</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>大卫迅速冲过去，伸手解开他手腕上的金属扣带。可就在他俯下身子，打算低头切断克拉克脚镣的瞬间，他的身体像被什么东西击中了一样僵住了。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=13</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>大卫</t>
+  </si>
+  <si>
+    <t>嘶——</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_David; 层级=14</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>他捂住头，左手按在太阳穴上，表情扭曲而痛苦，仿佛刚刚遭受电刑之苦的是他自己。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=15</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>你</t>
+  </si>
+  <si>
+    <t>怎么了？</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_You; 层级=16</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>大卫没有立刻回答。他用右手扶着椅背站稳，过了好几秒才慢慢松开按在额头上的手。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=17</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>你注意打他的眼神里有一瞬间的茫然闪过，但在落回到克拉克身上的那一刻，又触电似得恢复了之前的清明。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=18</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>可能是有点缺氧......等这次任务结束后，我说什么都得申请一次长达一个月的行政休假。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_David; 层级=19</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>这回可没人给我们开假条了，我们只能自己给自己开。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_You; 层级=20</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>你善意地提醒道，既然FBI的身份和这场梦境本身一样虚假，那么那所谓的行政休假自然也成了毫无意义的空头支票。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=21</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>切，真是多嘴。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_David; 层级=22</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>他一脸不悦地啐了一声，手上动作却没停，三下五除二地解开了克拉克身上最后一道绑带，另一只手稳稳扶住了对方发软的肩膀，尝试将这个大家伙从电椅上拉起身。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=23</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>喂？还回不回去了？你这臭小子，居然害我们找得这么辛苦，我这幅身子骨都快被你累散架了。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_David; 层级=24</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>克拉克张了张嘴，好半天才能挤出一点带着气音的沙哑声音，低着头，显然对自己被抓一事很是愧疚。</t>
+  </si>
+  <si>
+    <t>bgfade(sntzm_final(4)_28,1)</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=25</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>克拉克</t>
+  </si>
+  <si>
+    <t>抱歉，这次是我拖你们后腿了。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_Clark; 层级=26</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>现在说这些都已经不重要了，现在当务之急是从这个梦境里找到出去的办法。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_You; 层级=27</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>而被电成糨糊显然不属于其中之一。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_David; 层级=28</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>源类型=type:exeBC; 层级=29</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>大卫补充道，那令人熟悉的毒舌让维持了许久的压抑氛围终于得以稍稍放松，除了外面正仔细检查着另一个隔间的索菲亚。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=30; wherelist={"wheretype":"2","wheredatas":[{"sortnum":"1","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"端详飞蛾（大卫）","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]},{"sortnum":"2","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"立刻离开","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"0","dowlist4":[]}]}]}</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>索菲亚</t>
+  </si>
+  <si>
+    <t>这不应该......</t>
+  </si>
+  <si>
     <r>
-      <t>源类型</t>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>loadScript(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>sntzm_final(5)</t>
     </r>
     <r>
       <rPr>
@@ -105,7 +406,153 @@
         <rFont val="Calibri"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve">=type:txt_pb; </t>
+      <t>, 5)</t>
+    </r>
+  </si>
+  <si>
+    <t>源类型=type:txt_Sophia; 层级=31; gotomainline=终局（终2）_5</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>大卫适时地补充道，然后一脚踹开了那扇把你们隔离数十分钟的铁门。在你选择让克拉克的那一刻，无论物理上的隔阂还是记忆上的虚假，都已无法再切断这份被你重新建立起来的羁绊。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=30; wherelist={"wheretype":"1","wheredatas":[{"sortnum":"1","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"无视飞蛾（大卫）","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]},{"sortnum":"2","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"立刻离开","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]}]}</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>克拉克顺着扶手慢慢站直，目光从你们搀扶的躯体间向隔壁的包间漏出些许。或许是基于“探员”被训练出来的警惕，亦或是被迫害后积蓄未发的愤怒，他都无法立刻忽视这个曾让自己和同伴身处险境的威胁。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=31</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>Clark_default</t>
+  </si>
+  <si>
+    <t>......他不见了。</t>
+  </si>
+  <si>
+    <t>charfadein(L,1)</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_Clark; 层级=32</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>事实正如他所说，那个本应躺着一具焦尸的电椅上，此刻竟空无一物。他的生命，以及他存在的过的痕迹，都在这场并不光彩的审判中一并蒸发了。</t>
+  </si>
+  <si>
+    <t>parallel(charfadeout(L,1);bgfade(sntzm_final(4)_38,1))</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=33</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>只在椅面留下一滩带着焦糊味的浅褐色血渍，证明刚才那场触目惊心的行刑真的发生过。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=34</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>你看向那滩静静摊开的血渍，指尖还能感受到刚才整间手术室震颤的余韵，亚波伦最后那带着解脱的歌声仿佛还在耳边打转——其中蕴含的邪恶深意让你不寒而栗。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=35</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>David_default</t>
+  </si>
+  <si>
+    <t>等等，快看那里......有行字。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_David; 层级=36</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>他伸手一指，手电光延伸的尽头处果然浮现了一行清晰的字迹——由亚波伦的鲜血书写的字迹。</t>
+  </si>
+  <si>
+    <t>parallel(charfadeout(L,1);bgfade(sntzm_final(3)_104,1))</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=37</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>终点亦为起点，火焰即是笼网的终局。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_You; 层级=38</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>你轻声念出这行字，像是怕惊动了某个蛰伏于暗处的幽灵。大卫的左眼皮跳动了一下，那古灵精怪的大脑在亚波伦喋喋不休的思想灌输结束后终于重新上线，开始从各个角度思考它的深层内涵。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=39</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>会不会和盖亚之心的位置有关？</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_David; 层级=40</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>他慢慢松开扶着克拉克胳膊的手臂，尝试让他自己站稳脚跟。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=41</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>毕竟那是我们现在唯一还缺少的东西，如果那东西真像亚波伦说的那么玄乎，说不定能带我们从这场梦境中走出去。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_David; 层级=42</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>但它应该在哪儿？或者说它可能在哪儿？假设盖亚之心就是我们此程的终点，那起点指的又该是哪里？</t>
+  </si>
+  <si>
+    <r>
+      <t>charfadeout(L,1)&amp;loadScript(</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +560,7 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>层级</t>
+      <t>sntzm_final(5)</t>
     </r>
     <r>
       <rPr>
@@ -121,848 +568,484 @@
         <rFont val="Calibri"/>
         <charset val="134"/>
       </rPr>
-      <t>=1</t>
+      <t>, 4)</t>
     </r>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>choice(选择克拉克|jump(7))&amp;choice(选择亚波伦|jump(6))</t>
-  </si>
-  <si>
-    <t>源类型=type:selectBC; 层级=2</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=3</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你的指尖落在右侧的按钮上，不带一丝犹豫。 </t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=4</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>按下去的那一瞬间，你能感觉到整个房间都安静了一瞬——连亚波伦脸上的笑意都暂停了半秒。然后，电流声随之响起。如同某种无法避免、亦无法延迟的天罚，降临在了那个操弄人心的魔鬼身上。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=5</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>亚波伦的身体猛地一弓，喉间滚出一声压抑的闷哼，巨大的能量波动席卷了他的身体，顺着整间手术室的墙壁扩散开来，惨白的灯光开始疯狂闪烁，每一次明暗交替都带着电流滋啦的炸响。</t>
-  </si>
-  <si>
-    <t>bgfade(sntzm_final(3)_57,1)</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=6</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>这个一直以来从容不迫的男人，这一刻也终于露出了痛苦的表情，但他没有惨叫或是哀嚎，反而以一种解脱般的狂喜，轻轻哼唱起了《匹诺曹》的童谣。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=7</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>亚波伦</t>
-  </si>
-  <si>
-    <t>我曾被束缚，但现在自由了......我已无拘无束。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_Abaddon; 层级=8</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>他的声音在电流的杂音中断断续续地传出来，清晰、平静，像是正在经历某种他早就知晓结局的超凡仪式。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=9</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">但最终，这首在死神面前奏响的终曲也还是随着其身体机能的失控，逐渐消减、失真、融化，直到完全消失在持续的白噪音里。 </t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=10</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>你听到右侧隔间的灯光暗了一档。门锁解除的声音在同一刻响起——咔哒一声，像是某个被拧紧的阀门突然松动了一下。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=11</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你转过头，看见左侧隔间的铁门正在缓缓弹开，克拉克还坐在那把电椅上，但他的头已经微微抬起，目光模糊地穿过你们之间那段被灯光切割成两半的距离。 </t>
-  </si>
-  <si>
-    <t>bgfade(sntzm_final(4)_15,1)</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=12</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>大卫迅速冲过去，伸手解开他手腕上的金属扣带。可就在他俯下身子，打算低头切断克拉克脚镣的瞬间，他的身体像被什么东西击中了一样僵住了。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=13</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>大卫</t>
-  </si>
-  <si>
-    <t>嘶——</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_David; 层级=14</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>他捂住头，左手按在太阳穴上，表情扭曲而痛苦，仿佛刚刚遭受电刑之苦的是他自己。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=15</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>你</t>
-  </si>
-  <si>
-    <t>怎么了？</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_You; 层级=16</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>大卫没有立刻回答。他用右手扶着椅背站稳，过了好几秒才慢慢松开按在额头上的手。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=17</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>你注意打他的眼神里有一瞬间的茫然闪过，但在落回到克拉克身上的那一刻，又触电似得恢复了之前的清明。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=18</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>可能是有点缺氧......等这次任务结束后，我说什么都得申请一次长达一个月的行政休假。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_David; 层级=19</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>这回可没人给我们开假条了，我们只能自己给自己开。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_You; 层级=20</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>你善意地提醒道，既然FBI的身份和这场梦境本身一样虚假，那么那所谓的行政休假自然也成了毫无意义的空头支票。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=21</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>切，真是多嘴。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_David; 层级=22</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>他一脸不悦地啐了一声，手上动作却没停，三下五除二地解开了克拉克身上最后一道绑带，另一只手稳稳扶住了对方发软的肩膀，尝试将这个大家伙从电椅上拉起身。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=23</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>喂？还回不回去了？你这臭小子，居然害我们找得这么辛苦，我这幅身子骨都快被你累散架了。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_David; 层级=24</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>克拉克张了张嘴，好半天才能挤出一点带着气音的沙哑声音，低着头，显然对自己被抓一事很是愧疚。</t>
-  </si>
-  <si>
-    <t>bgfade(sntzm_final(4)_28,1)</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=25</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>克拉克</t>
-  </si>
-  <si>
-    <t>抱歉，这次是我拖你们后腿了。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_Clark; 层级=26</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>现在说这些都已经不重要了，现在当务之急是从这个梦境里找到出去的办法。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_You; 层级=27</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>而被电成糨糊显然不属于其中之一。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_David; 层级=28</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>源类型=type:exeBC; 层级=29</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>大卫补充道，那令人熟悉的毒舌让维持了许久的压抑氛围终于得以稍稍放松，除了外面正仔细检查着另一个隔间的索菲亚。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=30; wherelist={"wheretype":"2","wheredatas":[{"sortnum":"1","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"端详飞蛾（大卫）","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]},{"sortnum":"2","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"立刻离开","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"0","dowlist4":[]}]}]}</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>索菲亚</t>
-  </si>
-  <si>
-    <t>这不应该......</t>
-  </si>
-  <si>
-    <t>loadScript(终局（终2）_5, 1)</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_Sophia; 层级=31; gotomainline=终局（终2）_5</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>大卫适时地补充道，然后一脚踹开了那扇把你们隔离数十分钟的铁门。在你选择让克拉克的那一刻，无论物理上的隔阂还是记忆上的虚假，都已无法再切断这份被你重新建立起来的羁绊。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=30; wherelist={"wheretype":"1","wheredatas":[{"sortnum":"1","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"无视飞蛾（大卫）","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]},{"sortnum":"2","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"立刻离开","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]}]}</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>克拉克顺着扶手慢慢站直，目光从你们搀扶的躯体间向隔壁的包间漏出些许。或许是基于“探员”被训练出来的警惕，亦或是被迫害后积蓄未发的愤怒，他都无法立刻忽视这个曾让自己和同伴身处险境的威胁。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=31</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>......他不见了。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_Clark; 层级=32</t>
-  </si>
-  <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t>事实正如他所说，那个本应躺着一具焦尸的电椅上，此刻竟空无一物。他的生命，以及他存在的过的痕迹，都在这场并不光彩的审判中一并蒸发了。</t>
+    <t>源类型=type:txt_You; 层级=43; gotomainline=终局（终2）_4</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>你的指尖在左侧按钮的上方悬停了半秒——然后，在大卫来得及阻止你之前，迅速落了下去。</t>
+  </si>
+  <si>
+    <t>56</t>
+  </si>
+  <si>
+    <t>按下去的那一瞬间，一种近乎麻木的清醒裹挟了你全身的感官，左边是大卫惊怒的喝止，身后亚波伦带着了然的轻笑，只有时钟滴答声还在空旷的房间里清晰地回荡。</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>你知道自己依旧在乎克拉克，即便是在得知你们共同经历的过去只是一场彻头彻尾的谎言......但你实在太需要真相了——</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>关于姐姐的死因、关于你自己的真实过去，旧的伤疤和新的疑惑全都需要亚波伦的亲口解答才能被彻底抚平，而克拉克......这个在现实中可能根本和你毫无联系的陌生人，此刻已经再也没法给出任何回应了。</t>
+  </si>
+  <si>
+    <t>59</t>
+  </si>
+  <si>
+    <t>咔哒一声轻响从按钮下方传出，像是钥匙打开了锈死的锁孔。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=8</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>电流声在半个呼吸的延迟后炸开了。但不是从一侧，是从两侧。</t>
+  </si>
+  <si>
+    <t>61</t>
+  </si>
+  <si>
+    <t>你看到克拉克的身体猛地向上弹起，金属扣带在他手腕上勒出深色的印痕，他的头向后仰去，喉咙里挤出一声短促的、被电流碾碎的声响。</t>
+  </si>
+  <si>
+    <t>bgfade(sntzm_final(4)_61,1)</t>
+  </si>
+  <si>
+    <t>62</t>
+  </si>
+  <si>
+    <t>与此同时，右侧隔间里的亚波伦也弓起了脊背，那条白大褂在他抽搐的躯体上绷出一道道扭曲的褶皱。他的表情在电光中模糊成一团明暗交错的影子——有痛苦，但更多的是近乎狂喜的解脱。</t>
+  </si>
+  <si>
+    <t>63</t>
+  </si>
+  <si>
+    <t>你在做什么？你不能就这样......</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_You; 层级=12</t>
+  </si>
+  <si>
+    <t>64</t>
+  </si>
+  <si>
+    <t>你扑到了他的门边，像一头等待着被投喂的野兽，疯狂拍打着那扇隔绝真相的铁门，却对身后的大卫捂着头跪地的异常一无所知。</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
+    <t>或者说......在恶魔的有意垂钓下，除了名为真相的美味饵料外，你的眼睛已经看不见其他任何东西。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=14</t>
+  </si>
+  <si>
+    <t>66</t>
+  </si>
+  <si>
+    <t>你果然......没让我失望，我本以为......这件事会，更困难一些。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_Abaddon; 层级=15</t>
+  </si>
+  <si>
+    <t>67</t>
+  </si>
+  <si>
+    <t>他的声音在电流的杂音中断断续续地传出来，清晰、平静，没有回答你的任何提问，像是正在经历某种他早就知晓结局的超凡仪式，却对凡人信徒的寻求的启示置之不理。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=16</t>
+  </si>
+  <si>
+    <t>68</t>
+  </si>
+  <si>
+    <t>你看见他的手指在扶手上轻轻敲着拍子，像在指挥一支只有他自己能听见的乐队。</t>
+  </si>
+  <si>
+    <t>69</t>
+  </si>
+  <si>
+    <t xml:space="preserve">周围的灯光逐渐暗了下来——不是熄灭，而是那种电压被瞬间抽干后的、缓慢的昏黄。 </t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>等它再次稳定亮起时，亚波伦已经不在那把椅子上了。 没有尸体，没有烟雾。没有任何他存在过的痕迹。只有几根断裂的线缆从椅背后面垂下来，轻轻晃动，像是刚刚才被松开手。</t>
   </si>
   <si>
     <t>bgfade(sntzm_final(4)_38,1)</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=33</t>
-  </si>
-  <si>
-    <t>39</t>
-  </si>
-  <si>
-    <t>只在椅面留下一滩带着焦糊味的浅褐色血渍，证明刚才那场触目惊心的行刑真的发生过。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=34</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>你看向那滩静静摊开的血渍，指尖还能感受到刚才整间手术室震颤的余韵，亚波伦最后那带着解脱的歌声仿佛还在耳边打转——其中蕴含的邪恶深意让你不寒而栗。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=35</t>
-  </si>
-  <si>
-    <t>41</t>
-  </si>
-  <si>
-    <t>等等，快看那里......有行字。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_David; 层级=36</t>
-  </si>
-  <si>
-    <t>42</t>
-  </si>
-  <si>
-    <t>他伸手一指，手电光延伸的尽头处果然浮现了一行清晰的字迹——由亚波伦的鲜血书写的字迹。</t>
-  </si>
-  <si>
-    <t>bgfade(sntzm_final(3)_104,1)</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=37</t>
-  </si>
-  <si>
-    <t>43</t>
-  </si>
-  <si>
-    <t>终点亦为起点，火焰即是笼网的终局。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_You; 层级=38</t>
-  </si>
-  <si>
-    <t>44</t>
-  </si>
-  <si>
-    <t>你轻声念出这行字，像是怕惊动了某个蛰伏于暗处的幽灵。大卫的左眼皮跳动了一下，那古灵精怪的大脑在亚波伦喋喋不休的思想灌输结束后终于重新上线，开始从各个角度思考它的深层内涵。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=39</t>
-  </si>
-  <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>会不会和盖亚之心的位置有关？</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_David; 层级=40</t>
-  </si>
-  <si>
-    <t>46</t>
-  </si>
-  <si>
-    <t>他慢慢松开扶着克拉克胳膊的手臂，尝试让他自己站稳脚跟。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=41</t>
-  </si>
-  <si>
-    <t>47</t>
-  </si>
-  <si>
-    <t>毕竟那是我们现在唯一还缺少的东西，如果那东西真像亚波伦说的那么玄乎，说不定能带我们从这场梦境中走出去。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_David; 层级=42</t>
-  </si>
-  <si>
-    <t>48</t>
-  </si>
-  <si>
-    <t>但它应该在哪儿？或者说它可能在哪儿？假设盖亚之心就是我们此程的终点，那起点指的又该是哪里？</t>
-  </si>
-  <si>
-    <t>loadScript(终局（终2）_4, 1)</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_You; 层级=43; gotomainline=终局（终2）_4</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>loadScript(终局（终2）_2, 1)</t>
+    <t>源类型=type:txt_pb; 层级=19</t>
+  </si>
+  <si>
+    <t>71</t>
+  </si>
+  <si>
+    <t>不......</t>
+  </si>
+  <si>
+    <t>72</t>
+  </si>
+  <si>
+    <t>他消失了，但承诺应该还在。你付出了代价，他总该兑现些什么。</t>
+  </si>
+  <si>
+    <t>73</t>
+  </si>
+  <si>
+    <t>你推开右侧隔间的门，走进去。手电筒扫过那把空椅子，扫过椅背上残留的线缆，扫过扶手上一道被指甲刮出的浅痕......什么都没有。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=22</t>
+  </si>
+  <si>
+    <t>74</t>
+  </si>
+  <si>
+    <t>没有声音，没有话语，没有秘密——你像是把一枚硬币投进了一台早已被搬空的自动贩卖机里，却连回弹的声响都听不见。</t>
+  </si>
+  <si>
+    <t>75</t>
+  </si>
+  <si>
+    <t>你听见自己的呼吸开始变重。一种钝痛从胸腔深处慢慢胀开，像是什么东西被这份承诺勾住，又被沉默松开后的，反弹的余震。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=24</t>
+  </si>
+  <si>
+    <t>76</t>
+  </si>
+  <si>
+    <t>你付出了克拉克。你付出了他。而亚波伦只是像一场梦一样散开了，留给你一把还带着余温的、空无一人的椅子。</t>
+  </si>
+  <si>
+    <t>77</t>
+  </si>
+  <si>
+    <t>源类型=type:exeBC; 层级=26</t>
+  </si>
+  <si>
+    <t>78</t>
+  </si>
+  <si>
+    <t>可还未等你从这份强烈到足以把你碾碎的失落中缓过气来，有什么东西便悄无生息地顶住了你的后脑——冷、硬、带着金属的凉意，是大卫的枪口。</t>
+  </si>
+  <si>
+    <t>bgfade(sntzm_final(4)_78,1)</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=27; wherelist={"wheretype":"1","wheredatas":[{"sortnum":"1","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"无视飞蛾（大卫）","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]},{"sortnum":"2","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"立刻离开","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]}]}</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>大卫？</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_You; 层级=28</t>
+  </si>
+  <si>
+    <t>86</t>
+  </si>
+  <si>
+    <t>你的声音比预想中更轻，更低，带着自知犯错后基于愧疚的软弱。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=29</t>
+  </si>
+  <si>
+    <t>87</t>
+  </si>
+  <si>
+    <t>……你在做什么？</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_You; 层级=30</t>
+  </si>
+  <si>
+    <t>88</t>
+  </si>
+  <si>
+    <t>大卫//?</t>
+  </si>
+  <si>
+    <t>做和你一样的事情，亚当——亲手杀死一名自己的同伴。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_DVIF; 层级=31</t>
+  </si>
+  <si>
+    <t>89</t>
+  </si>
+  <si>
+    <t>回答你的，是大卫的声音，却又仿佛来自另一个人的灵魂。你当然能理解他对于牺牲同伴的愤怒，但依旧不敢相信这会是那个平日里嘴硬心软的前辈会做出来的行为。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=32</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>不用看了，他已经死透了。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_DVIF; 层级=33</t>
+  </si>
+  <si>
+    <t>91</t>
+  </si>
+  <si>
+    <t>大卫把你试图看向克拉克的目光重新掰正，语气中添上了几分熟悉的讥讽。</t>
+  </si>
+  <si>
+    <t>92</t>
+  </si>
+  <si>
+    <t>那个语调你刚才听了一整晚——从容、戏谑、带着一种刚刚完成某个实验记录后的满足感。</t>
+  </si>
+  <si>
+    <t>93</t>
+  </si>
+  <si>
+    <t>他完美地完成了自己的任务，不是吗？现在轮到我来兑现自己的承诺了。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_DVIF; 层级=36</t>
+  </si>
+  <si>
+    <t>94</t>
+  </si>
+  <si>
+    <t>亚波伦？！</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_You; 层级=37</t>
+  </si>
+  <si>
+    <t>95</t>
+  </si>
+  <si>
+    <t>可那怎么可能，他是你看着在那张电椅上烤得魂飞魄散的，事到如今......为什么会夺舍大卫的身体，又是在什么时候做到的这一点？</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=38</t>
+  </si>
+  <si>
+    <t>96</t>
+  </si>
+  <si>
+    <t>大卫//亚波伦</t>
+  </si>
+  <si>
+    <t>你看起来有些意外啊，亚当。但这不正是你自己选择的结果吗？你要我活下来，所以我如你所愿了，只不过是换了副模样。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_DVABL; 层级=39</t>
+  </si>
+  <si>
+    <t>97</t>
+  </si>
+  <si>
+    <t>你刚夺走了我的一名同伴，现在还想夺走第二个吗？！</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_You; 层级=40</t>
+  </si>
+  <si>
+    <t>98</t>
+  </si>
+  <si>
+    <t>你的这声怒吼与其说是对他罪行的控诉，倒更像一句无力的自我辩解，底气不足的声音撞冰冷的墙面上，没来得及回弹几下，便歪歪扭扭地沉到了地上。</t>
+  </si>
+  <si>
+    <t>99</t>
+  </si>
+  <si>
+    <t>不不不，是你杀死了自己的同伴。你刚刚亲自按下了那个电死克拉克的开关，记得吗？</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_DVABL; 层级=42</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>我给了你们选择的机会。但你和纳丁达克那些人一样——你们都选了同一边。你选了‘更有价值的那个’。你选了我。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_DVABL; 层级=43</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>他的枪口轻轻地向前推了一下，像是在逼迫你直面自己的良心。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>loadScript(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>sntzm_final(5)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>, 6)</t>
+    </r>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=44; gotomainline=终局（终2）_6</t>
+  </si>
+  <si>
+    <t>79</t>
+  </si>
+  <si>
+    <t>可还未等你从这份强烈到足以把你碾碎的失落中缓过气来，身后的便响起一声压抑的闷响。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=27</t>
+  </si>
+  <si>
+    <t>81</t>
+  </si>
+  <si>
+    <t>只听大门的方向传来一声金属的破裂声，一只黑影从中间的缝隙中疾闪而出。它的速度快到令人无法反应，目标却不是你或者大卫，而是挡在克拉克门边还未来得及发出一声尖叫的索菲亚。</t>
+  </si>
+  <si>
+    <t>bgfade(sntzm_final(4)_81,1)&amp;parallel(playsfx(RockBreak);shake(screen,10,0.5))</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=28</t>
+  </si>
+  <si>
+    <t>82</t>
+  </si>
+  <si>
+    <t>！</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_Sophia; 层级=29</t>
+  </si>
+  <si>
+    <t>83</t>
+  </si>
+  <si>
+    <t>一次呼吸之间，她的身体便被那名不速之客狠狠按在了地上，毫无怜惜和迟疑，像对待一块陈旧、廉价的破旧抹布。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=30</t>
+  </si>
+  <si>
+    <t>84</t>
+  </si>
+  <si>
+    <t>来者不是别人，正是亚波伦早已备在门外的阿兰.斯科特。它的脸依旧苍白如蜡，细长的手指狠狠扎进猎物的皮肤，索菲亚的挣扎在它绝对的力量面前显得无比微弱，连呼救声都被硬生生掐在了喉咙里。</t>
+  </si>
+  <si>
+    <t>85</t>
+  </si>
+  <si>
+    <t>你刚打算拔枪瞄准，有什么东西却更快一步地顶住了你的后脑——冷、硬、带着金属的凉意，是大卫的枪口。</t>
+  </si>
+  <si>
+    <t>jump(80)</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=32; gotomainline=80</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=1</t>
-  </si>
-  <si>
     <t>52</t>
   </si>
   <si>
-    <t>choice(选择大卫|jump(53))&amp;choice(选择亚波伦|jump(55))</t>
+    <t>choice(选择大卫|jump(53))&amp;choice(选择亚波伦|jump(54))</t>
   </si>
   <si>
     <t>53</t>
   </si>
   <si>
-    <t>loadScript(终局（终2）_3, 1)</t>
+    <r>
+      <t>loadScript(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>sntzm_final(5)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>, 3)</t>
+    </r>
   </si>
   <si>
     <t>54</t>
   </si>
   <si>
-    <t>55</t>
-  </si>
-  <si>
-    <t>你的指尖在左侧按钮的上方悬停了半秒——然后，在大卫来得及阻止你之前，迅速落了下去。</t>
-  </si>
-  <si>
-    <t>56</t>
-  </si>
-  <si>
-    <t>按下去的那一瞬间，一种近乎麻木的清醒裹挟了你全身的感官，左边是大卫惊怒的喝止，身后亚波伦带着了然的轻笑，只有时钟滴答声还在空旷的房间里清晰地回荡。</t>
-  </si>
-  <si>
-    <t>57</t>
-  </si>
-  <si>
-    <t>你知道自己依旧在乎克拉克，即便是在得知你们共同经历的过去只是一场彻头彻尾的谎言......但你实在太需要真相了——</t>
-  </si>
-  <si>
-    <t>58</t>
-  </si>
-  <si>
-    <t>关于姐姐的死因、关于你自己的真实过去，旧的伤疤和新的疑惑全都需要亚波伦的亲口解答才能被彻底抚平，而克拉克......这个在现实中可能根本和你毫无联系的陌生人，此刻已经再也没法给出任何回应了。</t>
-  </si>
-  <si>
-    <t>59</t>
-  </si>
-  <si>
-    <t>咔哒一声轻响从按钮下方传出，像是钥匙打开了锈死的锁孔。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=8</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
-    <t>电流声在半个呼吸的延迟后炸开了。但不是从一侧，是从两侧。</t>
-  </si>
-  <si>
-    <t>61</t>
-  </si>
-  <si>
-    <t>你看到克拉克的身体猛地向上弹起，金属扣带在他手腕上勒出深色的印痕，他的头向后仰去，喉咙里挤出一声短促的、被电流碾碎的声响。</t>
-  </si>
-  <si>
-    <t>bgfade(sntzm_final(4)_61,1)</t>
-  </si>
-  <si>
-    <t>62</t>
-  </si>
-  <si>
-    <t>与此同时，右侧隔间里的亚波伦也弓起了脊背，那条白大褂在他抽搐的躯体上绷出一道道扭曲的褶皱。他的表情在电光中模糊成一团明暗交错的影子——有痛苦，但更多的是近乎狂喜的解脱。</t>
-  </si>
-  <si>
-    <t>63</t>
-  </si>
-  <si>
-    <t>你在做什么？你不能就这样......</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_You; 层级=12</t>
-  </si>
-  <si>
-    <t>64</t>
-  </si>
-  <si>
-    <t>你扑到了他的门边，像一头等待着被投喂的野兽，疯狂拍打着那扇隔绝真相的铁门，却对身后的大卫捂着头跪地的异常一无所知。</t>
-  </si>
-  <si>
-    <t>65</t>
-  </si>
-  <si>
-    <t>或者说......在恶魔的有意垂钓下，除了名为真相的美味饵料外，你的眼睛已经看不见其他任何东西。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=14</t>
-  </si>
-  <si>
-    <t>66</t>
-  </si>
-  <si>
-    <t>你果然......没让我失望，我本以为......这件事会，更困难一些。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_Abaddon; 层级=15</t>
-  </si>
-  <si>
-    <t>67</t>
-  </si>
-  <si>
-    <t>他的声音在电流的杂音中断断续续地传出来，清晰、平静，没有回答你的任何提问，像是正在经历某种他早就知晓结局的超凡仪式，却对凡人信徒的寻求的启示置之不理。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=16</t>
-  </si>
-  <si>
-    <t>68</t>
-  </si>
-  <si>
-    <t>你看见他的手指在扶手上轻轻敲着拍子，像在指挥一支只有他自己能听见的乐队。</t>
-  </si>
-  <si>
-    <t>69</t>
-  </si>
-  <si>
-    <t xml:space="preserve">周围的灯光逐渐暗了下来——不是熄灭，而是那种电压被瞬间抽干后的、缓慢的昏黄。 </t>
-  </si>
-  <si>
-    <t>70</t>
-  </si>
-  <si>
-    <t>等它再次稳定亮起时，亚波伦已经不在那把椅子上了。 没有尸体，没有烟雾。没有任何他存在过的痕迹。只有几根断裂的线缆从椅背后面垂下来，轻轻晃动，像是刚刚才被松开手。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=19</t>
-  </si>
-  <si>
-    <t>71</t>
-  </si>
-  <si>
-    <t>不......</t>
-  </si>
-  <si>
-    <t>72</t>
-  </si>
-  <si>
-    <t>他消失了，但承诺应该还在。你付出了代价，他总该兑现些什么。</t>
-  </si>
-  <si>
-    <t>73</t>
-  </si>
-  <si>
-    <t>你推开右侧隔间的门，走进去。手电筒扫过那把空椅子，扫过椅背上残留的线缆，扫过扶手上一道被指甲刮出的浅痕......什么都没有。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=22</t>
-  </si>
-  <si>
-    <t>74</t>
-  </si>
-  <si>
-    <t>没有声音，没有话语，没有秘密——你像是把一枚硬币投进了一台早已被搬空的自动贩卖机里，却连回弹的声响都听不见。</t>
-  </si>
-  <si>
-    <t>75</t>
-  </si>
-  <si>
-    <t>你听见自己的呼吸开始变重。一种钝痛从胸腔深处慢慢胀开，像是什么东西被这份承诺勾住，又被沉默松开后的，反弹的余震。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=24</t>
-  </si>
-  <si>
-    <t>76</t>
-  </si>
-  <si>
-    <t>你付出了克拉克。你付出了他。而亚波伦只是像一场梦一样散开了，留给你一把还带着余温的、空无一人的椅子。</t>
-  </si>
-  <si>
-    <t>77</t>
-  </si>
-  <si>
-    <t>源类型=type:exeBC; 层级=26</t>
-  </si>
-  <si>
-    <t>78</t>
-  </si>
-  <si>
-    <t>可还未等你从这份强烈到足以把你碾碎的失落中缓过气来，有什么东西便悄无生息地顶住了你的后脑——冷、硬、带着金属的凉意，是大卫的枪口。</t>
-  </si>
-  <si>
-    <t>bgfade(sntzm_final(4)_78,1)</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=27; wherelist={"wheretype":"1","wheredatas":[{"sortnum":"1","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"无视飞蛾（大卫）","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]},{"sortnum":"2","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"立刻离开","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]}]}</t>
-  </si>
-  <si>
-    <t>80</t>
-  </si>
-  <si>
-    <t>大卫？</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_You; 层级=28</t>
-  </si>
-  <si>
-    <t>86</t>
-  </si>
-  <si>
-    <t>你的声音比预想中更轻，更低，带着自知犯错后基于愧疚的软弱。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=29</t>
-  </si>
-  <si>
-    <t>87</t>
-  </si>
-  <si>
-    <t>……你在做什么？</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_You; 层级=30</t>
-  </si>
-  <si>
-    <t>88</t>
-  </si>
-  <si>
-    <t>大卫//?</t>
-  </si>
-  <si>
-    <t>做和你一样的事情，亚当——亲手杀死一名自己的同伴。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_大卫//?; 层级=31</t>
-  </si>
-  <si>
-    <t>89</t>
-  </si>
-  <si>
-    <t>回答你的，是大卫的声音，却又仿佛来自另一个人的灵魂。你当然能理解他对于牺牲同伴的愤怒，但依旧不敢相信这会是那个平日里嘴硬心软的前辈会做出来的行为。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=32</t>
-  </si>
-  <si>
-    <t>90</t>
-  </si>
-  <si>
-    <t>不用看了，他已经死透了。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_大卫//?; 层级=33</t>
-  </si>
-  <si>
-    <t>91</t>
-  </si>
-  <si>
-    <t>大卫把你试图看向克拉克的目光重新掰正，语气中添上了几分熟悉的讥讽。</t>
-  </si>
-  <si>
-    <t>92</t>
-  </si>
-  <si>
-    <t>那个语调你刚才听了一整晚——从容、戏谑、带着一种刚刚完成某个实验记录后的满足感。</t>
-  </si>
-  <si>
-    <t>93</t>
-  </si>
-  <si>
-    <t>他完美地完成了自己的任务，不是吗？现在轮到我来兑现自己的承诺了。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_大卫//?; 层级=36</t>
-  </si>
-  <si>
-    <t>94</t>
-  </si>
-  <si>
-    <t>亚波伦？！</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_You; 层级=37</t>
-  </si>
-  <si>
-    <t>95</t>
-  </si>
-  <si>
-    <t>可那怎么可能，他是你看着在那张电椅上烤得魂飞魄散的，事到如今......为什么会夺舍大卫的身体，又是在什么时候做到的这一点？</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=38</t>
-  </si>
-  <si>
-    <t>96</t>
-  </si>
-  <si>
-    <t>大卫//亚波伦</t>
-  </si>
-  <si>
-    <t>你看起来有些意外啊，亚当。但这不正是你自己选择的结果吗？你要我活下来，所以我如你所愿了，只不过是换了副模样。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_大卫//亚波伦; 层级=39</t>
-  </si>
-  <si>
-    <t>97</t>
-  </si>
-  <si>
-    <t>你刚夺走了我的一名同伴，现在还想夺走第二个吗？！</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_You; 层级=40</t>
-  </si>
-  <si>
-    <t>98</t>
-  </si>
-  <si>
-    <t>你的这声怒吼与其说是对他罪行的控诉，倒更像一句无力的自我辩解，底气不足的声音撞冰冷的墙面上，没来得及回弹几下，便歪歪扭扭地沉到了地上。</t>
-  </si>
-  <si>
-    <t>99</t>
-  </si>
-  <si>
-    <t>不不不，是你杀死了自己的同伴。你刚刚亲自按下了那个电死克拉克的开关，记得吗？</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_大卫//亚波伦; 层级=42</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>我给了你们选择的机会。但你和纳丁达克那些人一样——你们都选了同一边。你选了‘更有价值的那个’。你选了我。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_大卫//亚波伦; 层级=43</t>
-  </si>
-  <si>
-    <t>101</t>
-  </si>
-  <si>
-    <t>他的枪口轻轻地向前推了一下，像是在逼迫你直面自己的良心。</t>
-  </si>
-  <si>
-    <t>loadScript(终局（终2）_6, 1)</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=44; gotomainline=终局（终2）_6</t>
-  </si>
-  <si>
-    <t>79</t>
-  </si>
-  <si>
-    <t>可还未等你从这份强烈到足以把你碾碎的失落中缓过气来，身后的便响起一声压抑的闷响。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=27</t>
-  </si>
-  <si>
-    <t>81</t>
-  </si>
-  <si>
-    <t>只听大门的方向传来一声金属的破裂声，一只黑影从中间的缝隙中疾闪而出。它的速度快到令人无法反应，目标却不是你或者大卫，而是挡在克拉克门边还未来得及发出一声尖叫的索菲亚。</t>
-  </si>
-  <si>
-    <t>bgfade(sntzm_final(4)_81,1)&amp;parallel(playsfx(RockBreak);shake(screen,10,0.5))</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=28</t>
-  </si>
-  <si>
-    <t>82</t>
-  </si>
-  <si>
-    <t>！</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_Sophia; 层级=29</t>
-  </si>
-  <si>
-    <t>83</t>
-  </si>
-  <si>
-    <t>一次呼吸之间，她的身体便被那名不速之客狠狠按在了地上，毫无怜惜和迟疑，像对待一块陈旧、廉价的破旧抹布。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=30</t>
-  </si>
-  <si>
-    <t>84</t>
-  </si>
-  <si>
-    <t>来者不是别人，正是亚波伦早已备在门外的阿兰.斯科特。它的脸依旧苍白如蜡，细长的手指狠狠扎进猎物的皮肤，索菲亚的挣扎在它绝对的力量面前显得无比微弱，连呼救声都被硬生生掐在了喉咙里。</t>
-  </si>
-  <si>
-    <t>85</t>
-  </si>
-  <si>
-    <t>你刚打算拔枪瞄准，有什么东西却更快一步地顶住了你的后脑——冷、硬、带着金属的凉意，是大卫的枪口。</t>
-  </si>
-  <si>
-    <t>jump(80)</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=32; gotomainline=80</t>
+    <r>
+      <t>loadScript(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>sntzm_final(5)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>, 2)</t>
+    </r>
   </si>
   <si>
     <t>项目</t>
@@ -974,13 +1057,13 @@
     <t>源 JSON</t>
   </si>
   <si>
-    <t>圣诺汀之梦_终局（终）.json</t>
+    <t>圣诺汀之梦_终局（终） (1).json</t>
   </si>
   <si>
     <t>转换时间</t>
   </si>
   <si>
-    <t>2026/8/31 17:50:22</t>
+    <t>2026/9/3 10:05:53</t>
   </si>
   <si>
     <t>输出节点数</t>
@@ -1539,11 +1622,6 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1696,6 +1774,11 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="34">
@@ -2004,28 +2087,31 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2034,129 +2120,127 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2435,7 +2519,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -2445,46 +2529,46 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Traditional Arabic"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
         <a:font script="Ethi" typeface="Nyala"/>
@@ -2509,17 +2593,16 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Traditional Arabic"/>
+        <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
         <a:font script="Ethi" typeface="Nyala"/>
@@ -2544,7 +2627,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -2556,131 +2638,160 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -2693,53 +2804,53 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L99"/>
-  <sheetFormatPr defaultColWidth="10.2857142857143" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="48" customWidth="1"/>
-    <col min="8" max="9" width="18" customWidth="1"/>
-    <col min="10" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="44" customWidth="1"/>
-    <col min="12" max="12" width="60" customWidth="1"/>
+    <col min="1" max="1" width="12" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18" style="1" customWidth="1"/>
+    <col min="3" max="6" width="14" style="1" customWidth="1"/>
+    <col min="7" max="7" width="48" style="1" customWidth="1"/>
+    <col min="8" max="9" width="18" style="1" customWidth="1"/>
+    <col min="10" max="10" width="12" style="1" customWidth="1"/>
+    <col min="11" max="11" width="44" style="1" customWidth="1"/>
+    <col min="12" max="12" width="60" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2815,7 +2926,7 @@
       <c r="K3" t="s">
         <v>15</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="L3" t="s">
         <v>20</v>
       </c>
     </row>
@@ -3952,7 +4063,7 @@
       <c r="J33" t="s">
         <v>15</v>
       </c>
-      <c r="K33" t="s">
+      <c r="K33" s="3" t="s">
         <v>116</v>
       </c>
       <c r="L33" t="s">
@@ -4046,7 +4157,7 @@
         <v>14</v>
       </c>
       <c r="D36" t="s">
-        <v>15</v>
+        <v>125</v>
       </c>
       <c r="E36" t="s">
         <v>15</v>
@@ -4055,7 +4166,7 @@
         <v>15</v>
       </c>
       <c r="G36" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H36" t="s">
         <v>15</v>
@@ -4067,15 +4178,15 @@
         <v>15</v>
       </c>
       <c r="K36" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
       <c r="L36" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="37" ht="40.5" spans="1:12">
       <c r="A37" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B37" t="s">
         <v>13</v>
@@ -4084,7 +4195,7 @@
         <v>14</v>
       </c>
       <c r="D37" t="s">
-        <v>15</v>
+        <v>125</v>
       </c>
       <c r="E37" t="s">
         <v>15</v>
@@ -4093,7 +4204,7 @@
         <v>15</v>
       </c>
       <c r="G37" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H37" t="s">
         <v>15</v>
@@ -4105,15 +4216,15 @@
         <v>15</v>
       </c>
       <c r="K37" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L37" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="38" ht="27" spans="1:12">
       <c r="A38" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B38" t="s">
         <v>13</v>
@@ -4131,7 +4242,7 @@
         <v>15</v>
       </c>
       <c r="G38" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H38" t="s">
         <v>15</v>
@@ -4146,12 +4257,12 @@
         <v>15</v>
       </c>
       <c r="L38" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="39" ht="55.5" spans="1:12">
       <c r="A39" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B39" t="s">
         <v>13</v>
@@ -4169,7 +4280,7 @@
         <v>15</v>
       </c>
       <c r="G39" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H39" t="s">
         <v>15</v>
@@ -4184,12 +4295,12 @@
         <v>15</v>
       </c>
       <c r="L39" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="40" spans="1:12">
       <c r="A40" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B40" t="s">
         <v>60</v>
@@ -4198,7 +4309,7 @@
         <v>14</v>
       </c>
       <c r="D40" t="s">
-        <v>15</v>
+        <v>140</v>
       </c>
       <c r="E40" t="s">
         <v>15</v>
@@ -4207,7 +4318,7 @@
         <v>15</v>
       </c>
       <c r="G40" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="H40" t="s">
         <v>15</v>
@@ -4219,15 +4330,15 @@
         <v>15</v>
       </c>
       <c r="K40" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
       <c r="L40" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="41" ht="28.5" spans="1:12">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="41" ht="30" spans="1:12">
       <c r="A41" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B41" t="s">
         <v>13</v>
@@ -4236,7 +4347,7 @@
         <v>14</v>
       </c>
       <c r="D41" t="s">
-        <v>15</v>
+        <v>140</v>
       </c>
       <c r="E41" t="s">
         <v>15</v>
@@ -4245,7 +4356,7 @@
         <v>15</v>
       </c>
       <c r="G41" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="H41" t="s">
         <v>15</v>
@@ -4257,15 +4368,15 @@
         <v>15</v>
       </c>
       <c r="K41" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="L41" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="42" spans="1:12">
       <c r="A42" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B42" t="s">
         <v>67</v>
@@ -4283,7 +4394,7 @@
         <v>15</v>
       </c>
       <c r="G42" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="H42" t="s">
         <v>15</v>
@@ -4298,12 +4409,12 @@
         <v>15</v>
       </c>
       <c r="L42" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="43" ht="54" spans="1:12">
       <c r="A43" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B43" t="s">
         <v>13</v>
@@ -4321,7 +4432,7 @@
         <v>15</v>
       </c>
       <c r="G43" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="H43" t="s">
         <v>15</v>
@@ -4336,12 +4447,12 @@
         <v>15</v>
       </c>
       <c r="L43" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="44" spans="1:12">
       <c r="A44" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B44" t="s">
         <v>60</v>
@@ -4350,7 +4461,7 @@
         <v>14</v>
       </c>
       <c r="D44" t="s">
-        <v>15</v>
+        <v>140</v>
       </c>
       <c r="E44" t="s">
         <v>15</v>
@@ -4359,7 +4470,7 @@
         <v>15</v>
       </c>
       <c r="G44" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="H44" t="s">
         <v>15</v>
@@ -4371,15 +4482,15 @@
         <v>15</v>
       </c>
       <c r="K44" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
       <c r="L44" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
     <row r="45" ht="27" spans="1:12">
       <c r="A45" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B45" t="s">
         <v>13</v>
@@ -4388,7 +4499,7 @@
         <v>14</v>
       </c>
       <c r="D45" t="s">
-        <v>15</v>
+        <v>140</v>
       </c>
       <c r="E45" t="s">
         <v>15</v>
@@ -4397,7 +4508,7 @@
         <v>15</v>
       </c>
       <c r="G45" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="H45" t="s">
         <v>15</v>
@@ -4412,12 +4523,12 @@
         <v>15</v>
       </c>
       <c r="L45" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="46" ht="40.5" spans="1:12">
       <c r="A46" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B46" t="s">
         <v>60</v>
@@ -4426,7 +4537,7 @@
         <v>14</v>
       </c>
       <c r="D46" t="s">
-        <v>15</v>
+        <v>140</v>
       </c>
       <c r="E46" t="s">
         <v>15</v>
@@ -4435,7 +4546,7 @@
         <v>15</v>
       </c>
       <c r="G46" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="H46" t="s">
         <v>15</v>
@@ -4450,12 +4561,12 @@
         <v>15</v>
       </c>
       <c r="L46" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="47" ht="40.5" spans="1:12">
       <c r="A47" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B47" t="s">
         <v>67</v>
@@ -4464,7 +4575,7 @@
         <v>14</v>
       </c>
       <c r="D47" t="s">
-        <v>15</v>
+        <v>140</v>
       </c>
       <c r="E47" t="s">
         <v>15</v>
@@ -4473,7 +4584,7 @@
         <v>15</v>
       </c>
       <c r="G47" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="H47" t="s">
         <v>15</v>
@@ -4484,16 +4595,16 @@
       <c r="J47" t="s">
         <v>15</v>
       </c>
-      <c r="K47" t="s">
-        <v>161</v>
+      <c r="K47" s="3" t="s">
+        <v>164</v>
       </c>
       <c r="L47" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="48" spans="1:12">
       <c r="A48" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B48" t="s">
         <v>13</v>
@@ -4522,16 +4633,14 @@
       <c r="J48" t="s">
         <v>15</v>
       </c>
-      <c r="K48" t="s">
-        <v>164</v>
-      </c>
+      <c r="K48"/>
       <c r="L48" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="49" spans="1:12">
+    <row r="49" ht="28.5" spans="1:12">
       <c r="A49" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B49" t="s">
         <v>13</v>
@@ -4549,7 +4658,7 @@
         <v>15</v>
       </c>
       <c r="G49" t="s">
-        <v>19</v>
+        <v>168</v>
       </c>
       <c r="H49" t="s">
         <v>15</v>
@@ -4564,12 +4673,12 @@
         <v>15</v>
       </c>
       <c r="L49" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="50" ht="30" spans="1:12">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="50" ht="54" spans="1:12">
       <c r="A50" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B50" t="s">
         <v>13</v>
@@ -4587,7 +4696,7 @@
         <v>15</v>
       </c>
       <c r="G50" t="s">
-        <v>15</v>
+        <v>170</v>
       </c>
       <c r="H50" t="s">
         <v>15</v>
@@ -4599,15 +4708,15 @@
         <v>15</v>
       </c>
       <c r="K50" t="s">
-        <v>168</v>
+        <v>15</v>
       </c>
       <c r="L50" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="51" ht="43.5" spans="1:12">
       <c r="A51" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B51" t="s">
         <v>13</v>
@@ -4625,7 +4734,7 @@
         <v>15</v>
       </c>
       <c r="G51" t="s">
-        <v>15</v>
+        <v>172</v>
       </c>
       <c r="H51" t="s">
         <v>15</v>
@@ -4637,15 +4746,15 @@
         <v>15</v>
       </c>
       <c r="K51" t="s">
-        <v>170</v>
+        <v>15</v>
       </c>
       <c r="L51" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="52" ht="69" spans="1:12">
       <c r="A52" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B52" t="s">
         <v>13</v>
@@ -4663,7 +4772,7 @@
         <v>15</v>
       </c>
       <c r="G52" t="s">
-        <v>15</v>
+        <v>174</v>
       </c>
       <c r="H52" t="s">
         <v>15</v>
@@ -4678,12 +4787,12 @@
         <v>15</v>
       </c>
       <c r="L52" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="53" ht="28.5" spans="1:12">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="53" ht="27" spans="1:12">
       <c r="A53" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B53" t="s">
         <v>13</v>
@@ -4701,7 +4810,7 @@
         <v>15</v>
       </c>
       <c r="G53" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="H53" t="s">
         <v>15</v>
@@ -4716,12 +4825,12 @@
         <v>15</v>
       </c>
       <c r="L53" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="54" ht="54" spans="1:12">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="54" ht="27" spans="1:12">
       <c r="A54" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B54" t="s">
         <v>13</v>
@@ -4739,7 +4848,7 @@
         <v>15</v>
       </c>
       <c r="G54" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="H54" t="s">
         <v>15</v>
@@ -4754,12 +4863,12 @@
         <v>15</v>
       </c>
       <c r="L54" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="55" ht="43.5" spans="1:12">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="55" ht="40.5" spans="1:12">
       <c r="A55" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B55" t="s">
         <v>13</v>
@@ -4777,7 +4886,7 @@
         <v>15</v>
       </c>
       <c r="G55" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="H55" t="s">
         <v>15</v>
@@ -4789,15 +4898,15 @@
         <v>15</v>
       </c>
       <c r="K55" t="s">
-        <v>15</v>
+        <v>182</v>
       </c>
       <c r="L55" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="56" ht="69" spans="1:12">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="56" ht="55.5" spans="1:12">
       <c r="A56" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="B56" t="s">
         <v>13</v>
@@ -4815,7 +4924,7 @@
         <v>15</v>
       </c>
       <c r="G56" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="H56" t="s">
         <v>15</v>
@@ -4830,15 +4939,15 @@
         <v>15</v>
       </c>
       <c r="L56" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="57" ht="27" spans="1:12">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12">
       <c r="A57" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="B57" t="s">
-        <v>13</v>
+        <v>67</v>
       </c>
       <c r="C57" t="s">
         <v>14</v>
@@ -4853,7 +4962,7 @@
         <v>15</v>
       </c>
       <c r="G57" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="H57" t="s">
         <v>15</v>
@@ -4868,12 +4977,12 @@
         <v>15</v>
       </c>
       <c r="L57" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="58" ht="27" spans="1:12">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="58" ht="40.5" spans="1:12">
       <c r="A58" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="B58" t="s">
         <v>13</v>
@@ -4891,7 +5000,7 @@
         <v>15</v>
       </c>
       <c r="G58" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="H58" t="s">
         <v>15</v>
@@ -4906,12 +5015,12 @@
         <v>15</v>
       </c>
       <c r="L58" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="59" ht="40.5" spans="1:12">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="59" ht="28.5" spans="1:12">
       <c r="A59" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B59" t="s">
         <v>13</v>
@@ -4929,7 +5038,7 @@
         <v>15</v>
       </c>
       <c r="G59" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="H59" t="s">
         <v>15</v>
@@ -4941,57 +5050,57 @@
         <v>15</v>
       </c>
       <c r="K59" t="s">
-        <v>187</v>
+        <v>15</v>
       </c>
       <c r="L59" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="60" ht="55.5" spans="1:12">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="60" ht="28.5" spans="1:12">
       <c r="A60" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="B60" t="s">
+        <v>40</v>
+      </c>
+      <c r="C60" t="s">
+        <v>14</v>
+      </c>
+      <c r="D60" t="s">
+        <v>15</v>
+      </c>
+      <c r="E60" t="s">
+        <v>15</v>
+      </c>
+      <c r="F60" t="s">
+        <v>15</v>
+      </c>
+      <c r="G60" t="s">
+        <v>194</v>
+      </c>
+      <c r="H60" t="s">
+        <v>15</v>
+      </c>
+      <c r="I60" t="s">
+        <v>15</v>
+      </c>
+      <c r="J60" t="s">
+        <v>15</v>
+      </c>
+      <c r="K60" t="s">
+        <v>15</v>
+      </c>
+      <c r="L60" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="61" ht="54" spans="1:12">
+      <c r="A61" t="s">
+        <v>196</v>
+      </c>
+      <c r="B61" t="s">
         <v>13</v>
       </c>
-      <c r="C60" t="s">
-        <v>14</v>
-      </c>
-      <c r="D60" t="s">
-        <v>15</v>
-      </c>
-      <c r="E60" t="s">
-        <v>15</v>
-      </c>
-      <c r="F60" t="s">
-        <v>15</v>
-      </c>
-      <c r="G60" t="s">
-        <v>189</v>
-      </c>
-      <c r="H60" t="s">
-        <v>15</v>
-      </c>
-      <c r="I60" t="s">
-        <v>15</v>
-      </c>
-      <c r="J60" t="s">
-        <v>15</v>
-      </c>
-      <c r="K60" t="s">
-        <v>15</v>
-      </c>
-      <c r="L60" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12">
-      <c r="A61" t="s">
-        <v>190</v>
-      </c>
-      <c r="B61" t="s">
-        <v>67</v>
-      </c>
       <c r="C61" t="s">
         <v>14</v>
       </c>
@@ -5005,7 +5114,7 @@
         <v>15</v>
       </c>
       <c r="G61" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="H61" t="s">
         <v>15</v>
@@ -5020,12 +5129,12 @@
         <v>15</v>
       </c>
       <c r="L61" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="62" ht="40.5" spans="1:12">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="62" ht="27" spans="1:12">
       <c r="A62" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="B62" t="s">
         <v>13</v>
@@ -5043,7 +5152,7 @@
         <v>15</v>
       </c>
       <c r="G62" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="H62" t="s">
         <v>15</v>
@@ -5058,12 +5167,12 @@
         <v>15</v>
       </c>
       <c r="L62" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="63" ht="28.5" spans="1:12">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="63" ht="30" spans="1:12">
       <c r="A63" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B63" t="s">
         <v>13</v>
@@ -5081,7 +5190,7 @@
         <v>15</v>
       </c>
       <c r="G63" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="H63" t="s">
         <v>15</v>
@@ -5096,15 +5205,15 @@
         <v>15</v>
       </c>
       <c r="L63" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="64" ht="28.5" spans="1:12">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="64" ht="55.5" spans="1:12">
       <c r="A64" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="B64" t="s">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="C64" t="s">
         <v>14</v>
@@ -5119,7 +5228,7 @@
         <v>15</v>
       </c>
       <c r="G64" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="H64" t="s">
         <v>15</v>
@@ -5131,18 +5240,18 @@
         <v>15</v>
       </c>
       <c r="K64" t="s">
-        <v>15</v>
+        <v>205</v>
       </c>
       <c r="L64" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="65" ht="54" spans="1:12">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12">
       <c r="A65" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="B65" t="s">
-        <v>13</v>
+        <v>67</v>
       </c>
       <c r="C65" t="s">
         <v>14</v>
@@ -5157,7 +5266,7 @@
         <v>15</v>
       </c>
       <c r="G65" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="H65" t="s">
         <v>15</v>
@@ -5172,12 +5281,12 @@
         <v>15</v>
       </c>
       <c r="L65" t="s">
-        <v>203</v>
+        <v>81</v>
       </c>
     </row>
     <row r="66" ht="27" spans="1:12">
       <c r="A66" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="B66" t="s">
         <v>13</v>
@@ -5195,7 +5304,7 @@
         <v>15</v>
       </c>
       <c r="G66" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="H66" t="s">
         <v>15</v>
@@ -5210,12 +5319,12 @@
         <v>15</v>
       </c>
       <c r="L66" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="67" ht="30" spans="1:12">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="67" ht="42" spans="1:12">
       <c r="A67" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="B67" t="s">
         <v>13</v>
@@ -5233,7 +5342,7 @@
         <v>15</v>
       </c>
       <c r="G67" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="H67" t="s">
         <v>15</v>
@@ -5244,14 +5353,16 @@
       <c r="J67" t="s">
         <v>15</v>
       </c>
-      <c r="K67"/>
+      <c r="K67" t="s">
+        <v>15</v>
+      </c>
       <c r="L67" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="68" ht="55.5" spans="1:12">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="68" ht="42" spans="1:12">
       <c r="A68" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="B68" t="s">
         <v>13</v>
@@ -5269,7 +5380,7 @@
         <v>15</v>
       </c>
       <c r="G68" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="H68" t="s">
         <v>15</v>
@@ -5281,18 +5392,18 @@
         <v>15</v>
       </c>
       <c r="K68" t="s">
-        <v>129</v>
+        <v>15</v>
       </c>
       <c r="L68" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="69" spans="1:12">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="69" ht="40.5" spans="1:12">
       <c r="A69" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="B69" t="s">
-        <v>67</v>
+        <v>13</v>
       </c>
       <c r="C69" t="s">
         <v>14</v>
@@ -5307,7 +5418,7 @@
         <v>15</v>
       </c>
       <c r="G69" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="H69" t="s">
         <v>15</v>
@@ -5322,12 +5433,12 @@
         <v>15</v>
       </c>
       <c r="L69" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="70" ht="27" spans="1:12">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="70" ht="40.5" spans="1:12">
       <c r="A70" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="B70" t="s">
         <v>13</v>
@@ -5345,7 +5456,7 @@
         <v>15</v>
       </c>
       <c r="G70" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="H70" t="s">
         <v>15</v>
@@ -5360,12 +5471,12 @@
         <v>15</v>
       </c>
       <c r="L70" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="71" ht="42" spans="1:12">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12">
       <c r="A71" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="B71" t="s">
         <v>13</v>
@@ -5383,7 +5494,7 @@
         <v>15</v>
       </c>
       <c r="G71" t="s">
-        <v>216</v>
+        <v>15</v>
       </c>
       <c r="H71" t="s">
         <v>15</v>
@@ -5398,12 +5509,12 @@
         <v>15</v>
       </c>
       <c r="L71" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="72" ht="42" spans="1:12">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="72" ht="150" spans="1:12">
       <c r="A72" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="B72" t="s">
         <v>13</v>
@@ -5421,7 +5532,7 @@
         <v>15</v>
       </c>
       <c r="G72" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="H72" t="s">
         <v>15</v>
@@ -5433,18 +5544,18 @@
         <v>15</v>
       </c>
       <c r="K72" t="s">
-        <v>15</v>
+        <v>225</v>
       </c>
       <c r="L72" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="73" ht="40.5" spans="1:12">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12">
       <c r="A73" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="B73" t="s">
-        <v>13</v>
+        <v>67</v>
       </c>
       <c r="C73" t="s">
         <v>14</v>
@@ -5459,7 +5570,7 @@
         <v>15</v>
       </c>
       <c r="G73" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="H73" t="s">
         <v>15</v>
@@ -5474,12 +5585,12 @@
         <v>15</v>
       </c>
       <c r="L73" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="74" ht="40.5" spans="1:12">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="74" ht="27" spans="1:12">
       <c r="A74" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="B74" t="s">
         <v>13</v>
@@ -5497,7 +5608,7 @@
         <v>15</v>
       </c>
       <c r="G74" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="H74" t="s">
         <v>15</v>
@@ -5512,168 +5623,168 @@
         <v>15</v>
       </c>
       <c r="L74" t="s">
-        <v>97</v>
+        <v>232</v>
       </c>
     </row>
     <row r="75" spans="1:12">
       <c r="A75" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="B75" t="s">
+        <v>67</v>
+      </c>
+      <c r="C75" t="s">
+        <v>14</v>
+      </c>
+      <c r="D75" t="s">
+        <v>15</v>
+      </c>
+      <c r="E75" t="s">
+        <v>15</v>
+      </c>
+      <c r="F75" t="s">
+        <v>15</v>
+      </c>
+      <c r="G75" t="s">
+        <v>234</v>
+      </c>
+      <c r="H75" t="s">
+        <v>15</v>
+      </c>
+      <c r="I75" t="s">
+        <v>15</v>
+      </c>
+      <c r="J75" t="s">
+        <v>15</v>
+      </c>
+      <c r="K75" t="s">
+        <v>15</v>
+      </c>
+      <c r="L75" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="76" ht="28.5" spans="1:12">
+      <c r="A76" t="s">
+        <v>236</v>
+      </c>
+      <c r="B76" t="s">
+        <v>237</v>
+      </c>
+      <c r="C76" t="s">
+        <v>14</v>
+      </c>
+      <c r="D76" t="s">
+        <v>15</v>
+      </c>
+      <c r="E76" t="s">
+        <v>15</v>
+      </c>
+      <c r="F76" t="s">
+        <v>15</v>
+      </c>
+      <c r="G76" t="s">
+        <v>238</v>
+      </c>
+      <c r="H76" t="s">
+        <v>15</v>
+      </c>
+      <c r="I76" t="s">
+        <v>15</v>
+      </c>
+      <c r="J76" t="s">
+        <v>15</v>
+      </c>
+      <c r="K76" t="s">
+        <v>15</v>
+      </c>
+      <c r="L76" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="77" ht="54" spans="1:12">
+      <c r="A77" t="s">
+        <v>240</v>
+      </c>
+      <c r="B77" t="s">
         <v>13</v>
       </c>
-      <c r="C75" t="s">
-        <v>14</v>
-      </c>
-      <c r="D75" t="s">
-        <v>15</v>
-      </c>
-      <c r="E75" t="s">
-        <v>15</v>
-      </c>
-      <c r="F75" t="s">
-        <v>15</v>
-      </c>
-      <c r="G75" t="s">
-        <v>15</v>
-      </c>
-      <c r="H75" t="s">
-        <v>15</v>
-      </c>
-      <c r="I75" t="s">
-        <v>15</v>
-      </c>
-      <c r="J75" t="s">
-        <v>15</v>
-      </c>
-      <c r="K75" t="s">
-        <v>15</v>
-      </c>
-      <c r="L75" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="76" ht="150" spans="1:12">
-      <c r="A76" t="s">
-        <v>227</v>
-      </c>
-      <c r="B76" t="s">
+      <c r="C77" t="s">
+        <v>14</v>
+      </c>
+      <c r="D77" t="s">
+        <v>15</v>
+      </c>
+      <c r="E77" t="s">
+        <v>15</v>
+      </c>
+      <c r="F77" t="s">
+        <v>15</v>
+      </c>
+      <c r="G77" t="s">
+        <v>241</v>
+      </c>
+      <c r="H77" t="s">
+        <v>15</v>
+      </c>
+      <c r="I77" t="s">
+        <v>15</v>
+      </c>
+      <c r="J77" t="s">
+        <v>15</v>
+      </c>
+      <c r="K77" t="s">
+        <v>15</v>
+      </c>
+      <c r="L77" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12">
+      <c r="A78" t="s">
+        <v>243</v>
+      </c>
+      <c r="B78" t="s">
+        <v>237</v>
+      </c>
+      <c r="C78" t="s">
+        <v>14</v>
+      </c>
+      <c r="D78" t="s">
+        <v>15</v>
+      </c>
+      <c r="E78" t="s">
+        <v>15</v>
+      </c>
+      <c r="F78" t="s">
+        <v>15</v>
+      </c>
+      <c r="G78" t="s">
+        <v>244</v>
+      </c>
+      <c r="H78" t="s">
+        <v>15</v>
+      </c>
+      <c r="I78" t="s">
+        <v>15</v>
+      </c>
+      <c r="J78" t="s">
+        <v>15</v>
+      </c>
+      <c r="K78" t="s">
+        <v>15</v>
+      </c>
+      <c r="L78" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="79" ht="27" spans="1:12">
+      <c r="A79" t="s">
+        <v>246</v>
+      </c>
+      <c r="B79" t="s">
         <v>13</v>
       </c>
-      <c r="C76" t="s">
-        <v>14</v>
-      </c>
-      <c r="D76" t="s">
-        <v>15</v>
-      </c>
-      <c r="E76" t="s">
-        <v>15</v>
-      </c>
-      <c r="F76" t="s">
-        <v>15</v>
-      </c>
-      <c r="G76" t="s">
-        <v>228</v>
-      </c>
-      <c r="H76" t="s">
-        <v>15</v>
-      </c>
-      <c r="I76" t="s">
-        <v>15</v>
-      </c>
-      <c r="J76" t="s">
-        <v>15</v>
-      </c>
-      <c r="K76" t="s">
-        <v>229</v>
-      </c>
-      <c r="L76" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="77" spans="1:12">
-      <c r="A77" t="s">
-        <v>231</v>
-      </c>
-      <c r="B77" t="s">
-        <v>67</v>
-      </c>
-      <c r="C77" t="s">
-        <v>14</v>
-      </c>
-      <c r="D77" t="s">
-        <v>15</v>
-      </c>
-      <c r="E77" t="s">
-        <v>15</v>
-      </c>
-      <c r="F77" t="s">
-        <v>15</v>
-      </c>
-      <c r="G77" t="s">
-        <v>232</v>
-      </c>
-      <c r="H77" t="s">
-        <v>15</v>
-      </c>
-      <c r="I77" t="s">
-        <v>15</v>
-      </c>
-      <c r="J77" t="s">
-        <v>15</v>
-      </c>
-      <c r="K77" t="s">
-        <v>15</v>
-      </c>
-      <c r="L77" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="78" ht="27" spans="1:12">
-      <c r="A78" t="s">
-        <v>234</v>
-      </c>
-      <c r="B78" t="s">
-        <v>13</v>
-      </c>
-      <c r="C78" t="s">
-        <v>14</v>
-      </c>
-      <c r="D78" t="s">
-        <v>15</v>
-      </c>
-      <c r="E78" t="s">
-        <v>15</v>
-      </c>
-      <c r="F78" t="s">
-        <v>15</v>
-      </c>
-      <c r="G78" t="s">
-        <v>235</v>
-      </c>
-      <c r="H78" t="s">
-        <v>15</v>
-      </c>
-      <c r="I78" t="s">
-        <v>15</v>
-      </c>
-      <c r="J78" t="s">
-        <v>15</v>
-      </c>
-      <c r="K78" t="s">
-        <v>15</v>
-      </c>
-      <c r="L78" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="79" spans="1:12">
-      <c r="A79" t="s">
-        <v>237</v>
-      </c>
-      <c r="B79" t="s">
-        <v>67</v>
-      </c>
       <c r="C79" t="s">
         <v>14</v>
       </c>
@@ -5687,7 +5798,7 @@
         <v>15</v>
       </c>
       <c r="G79" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="H79" t="s">
         <v>15</v>
@@ -5702,15 +5813,15 @@
         <v>15</v>
       </c>
       <c r="L79" t="s">
-        <v>239</v>
+        <v>135</v>
       </c>
     </row>
     <row r="80" ht="28.5" spans="1:12">
       <c r="A80" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="B80" t="s">
-        <v>241</v>
+        <v>13</v>
       </c>
       <c r="C80" t="s">
         <v>14</v>
@@ -5725,7 +5836,7 @@
         <v>15</v>
       </c>
       <c r="G80" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="H80" t="s">
         <v>15</v>
@@ -5740,15 +5851,15 @@
         <v>15</v>
       </c>
       <c r="L80" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="81" ht="54" spans="1:12">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="81" ht="27" spans="1:12">
       <c r="A81" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="B81" t="s">
-        <v>13</v>
+        <v>237</v>
       </c>
       <c r="C81" t="s">
         <v>14</v>
@@ -5763,7 +5874,7 @@
         <v>15</v>
       </c>
       <c r="G81" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="H81" t="s">
         <v>15</v>
@@ -5778,15 +5889,15 @@
         <v>15</v>
       </c>
       <c r="L81" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
     </row>
     <row r="82" spans="1:12">
       <c r="A82" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="B82" t="s">
-        <v>241</v>
+        <v>67</v>
       </c>
       <c r="C82" t="s">
         <v>14</v>
@@ -5801,7 +5912,7 @@
         <v>15</v>
       </c>
       <c r="G82" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="H82" t="s">
         <v>15</v>
@@ -5816,12 +5927,12 @@
         <v>15</v>
       </c>
       <c r="L82" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="83" ht="27" spans="1:12">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="83" ht="42" spans="1:12">
       <c r="A83" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="B83" t="s">
         <v>13</v>
@@ -5839,7 +5950,7 @@
         <v>15</v>
       </c>
       <c r="G83" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="H83" t="s">
         <v>15</v>
@@ -5854,15 +5965,15 @@
         <v>15</v>
       </c>
       <c r="L83" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="84" ht="28.5" spans="1:12">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="84" ht="40.5" spans="1:12">
       <c r="A84" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="B84" t="s">
-        <v>13</v>
+        <v>260</v>
       </c>
       <c r="C84" t="s">
         <v>14</v>
@@ -5877,7 +5988,7 @@
         <v>15</v>
       </c>
       <c r="G84" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="H84" t="s">
         <v>15</v>
@@ -5892,15 +6003,15 @@
         <v>15</v>
       </c>
       <c r="L84" t="s">
-        <v>136</v>
+        <v>262</v>
       </c>
     </row>
     <row r="85" ht="27" spans="1:12">
       <c r="A85" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="B85" t="s">
-        <v>241</v>
+        <v>67</v>
       </c>
       <c r="C85" t="s">
         <v>14</v>
@@ -5915,7 +6026,7 @@
         <v>15</v>
       </c>
       <c r="G85" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="H85" t="s">
         <v>15</v>
@@ -5930,15 +6041,15 @@
         <v>15</v>
       </c>
       <c r="L85" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="86" spans="1:12">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="86" ht="54" spans="1:12">
       <c r="A86" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="B86" t="s">
-        <v>67</v>
+        <v>13</v>
       </c>
       <c r="C86" t="s">
         <v>14</v>
@@ -5953,7 +6064,7 @@
         <v>15</v>
       </c>
       <c r="G86" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="H86" t="s">
         <v>15</v>
@@ -5968,16 +6079,16 @@
         <v>15</v>
       </c>
       <c r="L86" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="87" ht="42" spans="1:12">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="87" ht="27" spans="1:12">
       <c r="A87" t="s">
+        <v>268</v>
+      </c>
+      <c r="B87" t="s">
         <v>260</v>
       </c>
-      <c r="B87" t="s">
-        <v>13</v>
-      </c>
       <c r="C87" t="s">
         <v>14</v>
       </c>
@@ -5991,7 +6102,7 @@
         <v>15</v>
       </c>
       <c r="G87" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="H87" t="s">
         <v>15</v>
@@ -6006,15 +6117,15 @@
         <v>15</v>
       </c>
       <c r="L87" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="88" ht="40.5" spans="1:12">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="88" ht="43.5" spans="1:12">
       <c r="A88" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="B88" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="C88" t="s">
         <v>14</v>
@@ -6029,7 +6140,7 @@
         <v>15</v>
       </c>
       <c r="G88" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="H88" t="s">
         <v>15</v>
@@ -6044,15 +6155,15 @@
         <v>15</v>
       </c>
       <c r="L88" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
     </row>
     <row r="89" ht="27" spans="1:12">
       <c r="A89" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="B89" t="s">
-        <v>67</v>
+        <v>13</v>
       </c>
       <c r="C89" t="s">
         <v>14</v>
@@ -6067,7 +6178,7 @@
         <v>15</v>
       </c>
       <c r="G89" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="H89" t="s">
         <v>15</v>
@@ -6078,16 +6189,16 @@
       <c r="J89" t="s">
         <v>15</v>
       </c>
-      <c r="K89" t="s">
-        <v>15</v>
+      <c r="K89" s="3" t="s">
+        <v>276</v>
       </c>
       <c r="L89" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="90" ht="54" spans="1:12">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="90" ht="27" spans="1:12">
       <c r="A90" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="B90" t="s">
         <v>13</v>
@@ -6105,7 +6216,7 @@
         <v>15</v>
       </c>
       <c r="G90" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="H90" t="s">
         <v>15</v>
@@ -6120,15 +6231,15 @@
         <v>15</v>
       </c>
       <c r="L90" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="91" ht="27" spans="1:12">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="91" ht="54" spans="1:12">
       <c r="A91" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="B91" t="s">
-        <v>264</v>
+        <v>13</v>
       </c>
       <c r="C91" t="s">
         <v>14</v>
@@ -6143,7 +6254,7 @@
         <v>15</v>
       </c>
       <c r="G91" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="H91" t="s">
         <v>15</v>
@@ -6155,18 +6266,18 @@
         <v>15</v>
       </c>
       <c r="K91" t="s">
-        <v>15</v>
+        <v>283</v>
       </c>
       <c r="L91" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="92" ht="43.5" spans="1:12">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12">
       <c r="A92" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="B92" t="s">
-        <v>264</v>
+        <v>114</v>
       </c>
       <c r="C92" t="s">
         <v>14</v>
@@ -6181,7 +6292,7 @@
         <v>15</v>
       </c>
       <c r="G92" t="s">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="H92" t="s">
         <v>15</v>
@@ -6196,12 +6307,12 @@
         <v>15</v>
       </c>
       <c r="L92" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="93" ht="27" spans="1:12">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="93" ht="40.5" spans="1:12">
       <c r="A93" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="B93" t="s">
         <v>13</v>
@@ -6219,7 +6330,7 @@
         <v>15</v>
       </c>
       <c r="G93" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="H93" t="s">
         <v>15</v>
@@ -6231,15 +6342,15 @@
         <v>15</v>
       </c>
       <c r="K93" t="s">
-        <v>280</v>
+        <v>15</v>
       </c>
       <c r="L93" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="94" ht="27" spans="1:12">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="94" ht="69" spans="1:12">
       <c r="A94" t="s">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="B94" t="s">
         <v>13</v>
@@ -6257,7 +6368,7 @@
         <v>15</v>
       </c>
       <c r="G94" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="H94" t="s">
         <v>15</v>
@@ -6272,12 +6383,12 @@
         <v>15</v>
       </c>
       <c r="L94" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="95" ht="54" spans="1:12">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="95" ht="42" spans="1:12">
       <c r="A95" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="B95" t="s">
         <v>13</v>
@@ -6295,7 +6406,7 @@
         <v>15</v>
       </c>
       <c r="G95" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="H95" t="s">
         <v>15</v>
@@ -6307,18 +6418,18 @@
         <v>15</v>
       </c>
       <c r="K95" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="L95" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
     </row>
     <row r="96" spans="1:12">
       <c r="A96" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="B96" t="s">
-        <v>114</v>
+        <v>13</v>
       </c>
       <c r="C96" t="s">
         <v>14</v>
@@ -6333,7 +6444,7 @@
         <v>15</v>
       </c>
       <c r="G96" t="s">
-        <v>290</v>
+        <v>19</v>
       </c>
       <c r="H96" t="s">
         <v>15</v>
@@ -6348,12 +6459,12 @@
         <v>15</v>
       </c>
       <c r="L96" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="97" ht="40.5" spans="1:12">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="97" ht="30" spans="1:12">
       <c r="A97" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="B97" t="s">
         <v>13</v>
@@ -6371,7 +6482,7 @@
         <v>15</v>
       </c>
       <c r="G97" t="s">
-        <v>293</v>
+        <v>15</v>
       </c>
       <c r="H97" t="s">
         <v>15</v>
@@ -6383,15 +6494,15 @@
         <v>15</v>
       </c>
       <c r="K97" t="s">
-        <v>15</v>
+        <v>299</v>
       </c>
       <c r="L97" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="98" ht="69" spans="1:12">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12">
       <c r="A98" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="B98" t="s">
         <v>13</v>
@@ -6409,7 +6520,7 @@
         <v>15</v>
       </c>
       <c r="G98" t="s">
-        <v>296</v>
+        <v>15</v>
       </c>
       <c r="H98" t="s">
         <v>15</v>
@@ -6420,16 +6531,16 @@
       <c r="J98" t="s">
         <v>15</v>
       </c>
-      <c r="K98" t="s">
-        <v>15</v>
+      <c r="K98" s="3" t="s">
+        <v>301</v>
       </c>
       <c r="L98" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="99" ht="42" spans="1:12">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12">
       <c r="A99" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="B99" t="s">
         <v>13</v>
@@ -6447,7 +6558,7 @@
         <v>15</v>
       </c>
       <c r="G99" t="s">
-        <v>298</v>
+        <v>15</v>
       </c>
       <c r="H99" t="s">
         <v>15</v>
@@ -6458,11 +6569,11 @@
       <c r="J99" t="s">
         <v>15</v>
       </c>
-      <c r="K99" t="s">
-        <v>299</v>
+      <c r="K99" s="3" t="s">
+        <v>303</v>
       </c>
       <c r="L99" t="s">
-        <v>300</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -6475,47 +6586,47 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:B15"/>
-  <sheetFormatPr defaultColWidth="10.2857142857143" defaultRowHeight="15" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="1" max="1" width="12" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>302</v>
+      <c r="A1" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="2" ht="30" spans="1:2">
       <c r="A2" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="B2" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B3" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B4" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="B5" t="s">
         <v>18</v>
@@ -6523,15 +6634,15 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="B6" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="7" ht="27" spans="1:2">
       <c r="A7" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
@@ -6539,7 +6650,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B8" t="s">
         <v>102</v>
@@ -6547,58 +6658,58 @@
     </row>
     <row r="9" ht="27" spans="1:2">
       <c r="A9" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B9" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10" ht="75" spans="1:2">
       <c r="A10" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B10" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="11" ht="75" spans="1:2">
       <c r="A11" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B11" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="12" ht="57" spans="1:2">
       <c r="A12" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B12" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:2">
       <c r="A13" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B13" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="14" ht="60" spans="1:2">
       <c r="A14" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B14" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="15" ht="75" spans="1:2">
       <c r="A15" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B15" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
   </sheetData>
@@ -6611,625 +6722,625 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F31"/>
-  <sheetFormatPr defaultColWidth="10.2857142857143" defaultRowHeight="15" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="6" width="14" customWidth="1"/>
+    <col min="1" max="1" width="12" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18" style="1" customWidth="1"/>
+    <col min="3" max="6" width="14" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>325</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="2" ht="73.5" spans="1:6">
       <c r="A2" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B2" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="C2" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D2" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="E2" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="F2" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="3" ht="103.5" spans="1:6">
       <c r="A3" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B3" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C3" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="D3" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="E3" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="F3" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="4" ht="45" spans="1:6">
       <c r="A4" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B4" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="C4" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="D4" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="E4" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="F4" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="5" ht="45" spans="1:6">
       <c r="A5" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B5" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="C5" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="D5" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="E5" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="F5" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="6" ht="45" spans="1:6">
       <c r="A6" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B6" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C6" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="D6" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="E6" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="F6" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="7" ht="75" spans="1:6">
       <c r="A7" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B7" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="C7" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="D7" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="E7" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="F7" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="8" ht="45" spans="1:6">
       <c r="A8" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B8" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="C8" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="D8" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="E8" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="F8" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="9" ht="45" spans="1:6">
       <c r="A9" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B9" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C9" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="D9" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="E9" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="F9" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="10" ht="58.5" spans="1:6">
       <c r="A10" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B10" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="C10" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="D10" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="E10" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="F10" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="11" ht="60" spans="1:6">
       <c r="A11" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B11" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C11" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="D11" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="E11" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="F11" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="12" ht="58.5" spans="1:6">
       <c r="A12" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B12" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="C12" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="D12" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="E12" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="F12" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:6">
       <c r="A13" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B13" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="C13" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="D13" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="E13" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="F13" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="14" ht="58.5" spans="1:6">
       <c r="A14" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B14" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="C14" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="D14" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="E14" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="F14" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="15" ht="58.5" spans="1:6">
       <c r="A15" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B15" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="C15" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="D15" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="E15" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="F15" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="16" ht="58.5" spans="1:6">
       <c r="A16" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B16" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="C16" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="D16" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="E16" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="F16" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="17" ht="58.5" spans="1:6">
       <c r="A17" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B17" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="C17" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="D17" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="E17" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="F17" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="18" ht="58.5" spans="1:6">
       <c r="A18" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B18" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="C18" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="D18" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="E18" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="F18" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="19" ht="58.5" spans="1:6">
       <c r="A19" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B19" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C19" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="D19" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E19" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="F19" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:6">
       <c r="A20" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B20" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="C20" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="D20" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="E20" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="F20" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="21" ht="58.5" spans="1:6">
       <c r="A21" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B21" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C21" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="D21" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="E21" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="F21" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="22" ht="58.5" spans="1:6">
       <c r="A22" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B22" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="C22" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="D22" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="E22" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="F22" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="23" ht="58.5" spans="1:6">
       <c r="A23" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B23" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C23" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="D23" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="E23" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="F23" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="24" ht="58.5" spans="1:6">
       <c r="A24" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B24" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C24" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="D24" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="E24" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="F24" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="25" ht="90" spans="1:6">
       <c r="A25" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="B25" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="C25" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="D25" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="E25" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="F25" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="26" ht="58.5" spans="1:6">
       <c r="A26" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="B26" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="C26" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="D26" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="E26" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="F26" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="27" ht="58.5" spans="1:6">
       <c r="A27" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="B27" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="C27" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D27" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="E27" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="F27" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="28" ht="58.5" spans="1:6">
       <c r="A28" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="B28" t="s">
+        <v>462</v>
+      </c>
+      <c r="C28" t="s">
+        <v>463</v>
+      </c>
+      <c r="D28" t="s">
         <v>459</v>
       </c>
-      <c r="C28" t="s">
-        <v>460</v>
-      </c>
-      <c r="D28" t="s">
-        <v>456</v>
-      </c>
       <c r="E28" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="F28" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="29" ht="73.5" spans="1:6">
       <c r="A29" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="B29" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="C29" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="D29" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="E29" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="F29" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="30" ht="58.5" spans="1:6">
       <c r="A30" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="B30" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="C30" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="D30" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="E30" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="F30" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="B31" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="C31" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="D31" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
   </sheetData>
